--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.30.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.30.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.30.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.30.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.30.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.30.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0030.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0030.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Orders:â€”</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: Orders:â€” -*</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]£3</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]£3</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L12: isolated marker/symbol line :: 0</t>
@@ -614,13 +618,13 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 95</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]£3</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: Orders:â€” -*</t>
+          <t>L30: punctuation artifact: hyphen/bullet debris :: Orders:— -*</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -654,11 +658,7 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
@@ -667,7 +667,11 @@
           <t>L14: isolated marker/symbol line :: 23</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L118: isolated marker/symbol line :: 95</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -730,12 +734,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -793,7 +797,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -933,7 +937,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1016,7 +1020,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
